--- a/data/trans_orig/IP2906_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>34994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52889</t>
+          <t>53129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29161</t>
+          <t>29581</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>48766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70144</t>
+          <t>70843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96492</t>
+          <t>97076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47251</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64215</t>
+          <t>65146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83932</t>
+          <t>83900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103505</t>
+          <t>103085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136314</t>
+          <t>135730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162662</t>
+          <t>161963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,57%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33209</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>48658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29589</t>
+          <t>29997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46621</t>
+          <t>46064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66474</t>
+          <t>66859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90059</t>
+          <t>89974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44451</t>
+          <t>44734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60183</t>
+          <t>59866</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46623</t>
+          <t>47180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63655</t>
+          <t>63247</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96578</t>
+          <t>96663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120163</t>
+          <t>119778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,18%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25496</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36402</t>
+          <t>36579</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>40160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58368</t>
+          <t>58825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22953</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34496</t>
+          <t>33567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40534</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52415</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71103</t>
+          <t>70623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64520</t>
+          <t>65119</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89013</t>
+          <t>89304</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83106</t>
+          <t>83181</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113792</t>
+          <t>111596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155493</t>
+          <t>154465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194874</t>
+          <t>194712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96588</t>
+          <t>96297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121081</t>
+          <t>120482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97114</t>
+          <t>99310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127800</t>
+          <t>127725</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201633</t>
+          <t>201795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241014</t>
+          <t>242042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>61264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52426</t>
+          <t>52172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81609</t>
+          <t>80031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100715</t>
+          <t>100578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136251</t>
+          <t>135954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53027</t>
+          <t>53536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71761</t>
+          <t>73408</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77852</t>
+          <t>79430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107035</t>
+          <t>107289</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138010</t>
+          <t>138307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173546</t>
+          <t>173683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22962</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37218</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45087</t>
+          <t>45394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57615</t>
+          <t>57122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78144</t>
+          <t>78182</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30172</t>
+          <t>29350</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>43950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22981</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>38296</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57314</t>
+          <t>57276</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77843</t>
+          <t>78336</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,83%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>243478</t>
+          <t>243883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>288152</t>
+          <t>287020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>282923</t>
+          <t>280907</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>337371</t>
+          <t>336297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>541388</t>
+          <t>538490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>609099</t>
+          <t>605228</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,29%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>321620</t>
+          <t>322752</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>366294</t>
+          <t>365889</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>389308</t>
+          <t>390382</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>443756</t>
+          <t>445772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>727353</t>
+          <t>731224</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>795064</t>
+          <t>797962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2906_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>36514</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29093</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47343</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,85%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44613</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34994</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>53129</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44,55%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38844</t>
+          <t>44392</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29581</t>
+          <t>36469</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>53041</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>83457</t>
+          <t>80906</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>70843</t>
+          <t>69666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97076</t>
+          <t>92941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82276</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>71447</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>89697</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>75,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55527</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47011</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>65146</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>55,45%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,06%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>93822</t>
+          <t>54373</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83900</t>
+          <t>45724</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103085</t>
+          <t>62296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>149349</t>
+          <t>136648</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135730</t>
+          <t>124613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161963</t>
+          <t>147888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118790</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>100140</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>98765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>232806</t>
+          <t>217554</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36016</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27765</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44366</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>40,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>49,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>40995</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33526</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>48658</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>43,9%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29997</t>
+          <t>33403</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46064</t>
+          <t>50533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>78756</t>
+          <t>77674</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66859</t>
+          <t>66717</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89974</t>
+          <t>90109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53457</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45107</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>61708</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>59,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>50,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52397</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>44734</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59866</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>56,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>64,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>55483</t>
+          <t>53752</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47180</t>
+          <t>44877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>62007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>107881</t>
+          <t>107209</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96663</t>
+          <t>94774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119778</t>
+          <t>118166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89473</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89473</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89473</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>186637</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>186637</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>186637</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26711</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19847</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32697</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20198</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14882</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26169</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29049</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49247</t>
+          <t>48393</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40160</t>
+          <t>40056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58825</t>
+          <t>57139</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29133</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23147</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35997</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>52,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>28251</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22280</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>33567</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>58,31%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>45,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,28%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33285</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40611</t>
+          <t>33743</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>57182</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>48436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70623</t>
+          <t>65519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>48449</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>48449</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>48449</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>49731</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>110783</t>
+          <t>105575</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110783</t>
+          <t>105575</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110783</t>
+          <t>105575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>90956</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>76774</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>105868</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>77049</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>65119</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>89304</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>41,51%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>48,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>97424</t>
+          <t>73596</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83181</t>
+          <t>62606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111596</t>
+          <t>84089</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>174473</t>
+          <t>164552</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154465</t>
+          <t>147347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>194712</t>
+          <t>181806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>104653</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>89741</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>118835</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>108552</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>96297</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>120482</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>58,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>113482</t>
+          <t>97033</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99310</t>
+          <t>86540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127725</t>
+          <t>108023</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>222034</t>
+          <t>201687</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201795</t>
+          <t>184433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242042</t>
+          <t>218892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>195609</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>195609</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>195609</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>185601</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>185601</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>185601</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>170629</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>170629</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>210906</t>
+          <t>170629</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>396507</t>
+          <t>366239</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>396507</t>
+          <t>366239</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>396507</t>
+          <t>366239</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>64549</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>49949</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>76764</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>44,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>51799</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>41392</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>61264</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>45,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>67736</t>
+          <t>49642</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52172</t>
+          <t>41162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80031</t>
+          <t>59584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>119535</t>
+          <t>114191</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100578</t>
+          <t>98954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135954</t>
+          <t>129057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>81037</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68822</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>95637</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>55,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>47,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>63001</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>53536</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>73408</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>54,88%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>46,63%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91725</t>
+          <t>64998</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79430</t>
+          <t>55056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107289</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>154726</t>
+          <t>146035</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138307</t>
+          <t>131169</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173683</t>
+          <t>161272</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>61,97%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>114800</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>114800</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>114800</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>114640</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>114640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>114640</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274261</t>
+          <t>260226</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274261</t>
+          <t>260226</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274261</t>
+          <t>260226</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>37662</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>29716</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>44324</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>58,02%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>45,78%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>68,28%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>30090</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>23440</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>38040</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>44,65%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>34,78%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>56,45%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37782</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29772</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>39763</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>67872</t>
+          <t>69376</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57122</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78182</t>
+          <t>79527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>27248</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>20586</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>35194</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>41,98%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>31,72%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>54,22%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>37300</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>29350</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>43950</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>55,35%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>43,55%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>65,22%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>30286</t>
+          <t>37048</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>44188</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>64297</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57276</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78336</t>
+          <t>74054</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64910</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64910</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64910</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>67390</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>67390</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>67390</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68068</t>
+          <t>68763</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>135458</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>135458</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>135458</t>
+          <t>133673</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>292407</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>267384</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>316979</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>43,63%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>39,9%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>396</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>264745</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>243883</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>287020</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>47,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>308595</t>
+          <t>262685</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>280907</t>
+          <t>241268</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>336297</t>
+          <t>283763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>573341</t>
+          <t>555093</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>538490</t>
+          <t>523500</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>605228</t>
+          <t>587930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>377805</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>353233</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>402828</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>56,37%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>52,7%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>60,1%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>496</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>345027</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>322752</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>365889</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>56,58%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>52,93%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>418084</t>
+          <t>335253</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>390382</t>
+          <t>314175</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>445772</t>
+          <t>356670</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>763111</t>
+          <t>713057</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>731224</t>
+          <t>680220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>797962</t>
+          <t>744650</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>58,72%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>670212</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>670212</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>670212</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>892</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>609772</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>609772</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>609772</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>915</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>726679</t>
+          <t>597938</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>726679</t>
+          <t>597938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>726679</t>
+          <t>597938</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1336452</t>
+          <t>1268150</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1336452</t>
+          <t>1268150</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1336452</t>
+          <t>1268150</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
